--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.45570642541806</v>
+        <v>7.549052294130436</v>
       </c>
       <c r="D2" t="n">
-        <v>46.24038453524227</v>
+        <v>7.51406248697687</v>
       </c>
       <c r="E2" t="n">
-        <v>11.16293790560471</v>
+        <v>1.813977409660765</v>
       </c>
       <c r="F2" t="n">
-        <v>11.33598845234264</v>
+        <v>1.842098123505679</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.02488421129018</v>
+        <v>7.316543684334654</v>
       </c>
       <c r="D3" t="n">
-        <v>45.26566530614159</v>
+        <v>7.355670612248009</v>
       </c>
       <c r="E3" t="n">
-        <v>11.16293790560471</v>
+        <v>1.813977409660765</v>
       </c>
       <c r="F3" t="n">
-        <v>11.33598845234264</v>
+        <v>1.842098123505679</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.2745170208668</v>
+        <v>6.382109015890856</v>
       </c>
       <c r="D4" t="n">
-        <v>38.03319275701873</v>
+        <v>6.180393823015544</v>
       </c>
       <c r="E4" t="n">
-        <v>11.16293790560471</v>
+        <v>1.813977409660765</v>
       </c>
       <c r="F4" t="n">
-        <v>11.33598845234264</v>
+        <v>1.842098123505679</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.99890553237598</v>
+        <v>8.124822149011097</v>
       </c>
       <c r="D5" t="n">
-        <v>39.24498528286725</v>
+        <v>6.377310108465929</v>
       </c>
       <c r="E5" t="n">
-        <v>11.16293790560471</v>
+        <v>1.813977409660765</v>
       </c>
       <c r="F5" t="n">
-        <v>11.33598845234264</v>
+        <v>1.842098123505679</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.65764369124344</v>
+        <v>6.28186709982706</v>
       </c>
       <c r="D6" t="n">
-        <v>38.97918969246196</v>
+        <v>6.334118325025068</v>
       </c>
       <c r="E6" t="n">
-        <v>11.16293790560471</v>
+        <v>1.813977409660765</v>
       </c>
       <c r="F6" t="n">
-        <v>11.33598845234264</v>
+        <v>1.842098123505679</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.55157545780806</v>
+        <v>5.777131011893809</v>
       </c>
       <c r="D7" t="n">
-        <v>36.64537799128674</v>
+        <v>5.954873923584096</v>
       </c>
       <c r="E7" t="n">
-        <v>11.16293790560471</v>
+        <v>1.813977409660765</v>
       </c>
       <c r="F7" t="n">
-        <v>11.33598845234264</v>
+        <v>1.842098123505679</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.20522679871156</v>
+        <v>2.958349354790628</v>
       </c>
       <c r="D8" t="n">
-        <v>16.7349787999987</v>
+        <v>2.719434054999788</v>
       </c>
       <c r="E8" t="n">
-        <v>11.16293790560471</v>
+        <v>1.813977409660765</v>
       </c>
       <c r="F8" t="n">
-        <v>11.33598845234264</v>
+        <v>1.842098123505679</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.87931293907373</v>
+        <v>4.042888352599482</v>
       </c>
       <c r="D9" t="n">
-        <v>24.92539109875933</v>
+        <v>4.050376053548392</v>
       </c>
       <c r="E9" t="n">
-        <v>11.16293790560471</v>
+        <v>1.813977409660765</v>
       </c>
       <c r="F9" t="n">
-        <v>11.33598845234264</v>
+        <v>1.842098123505679</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.53735158011164</v>
+        <v>2.849819631768141</v>
       </c>
       <c r="D10" t="n">
-        <v>11.66364566012766</v>
+        <v>1.895342419770744</v>
       </c>
       <c r="E10" t="n">
-        <v>11.16293790560471</v>
+        <v>1.813977409660765</v>
       </c>
       <c r="F10" t="n">
-        <v>11.33598845234264</v>
+        <v>1.842098123505679</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.36889099745302</v>
+        <v>4.284944787086116</v>
       </c>
       <c r="D11" t="n">
-        <v>24.84943428064605</v>
+        <v>4.038033070604984</v>
       </c>
       <c r="E11" t="n">
-        <v>11.16293790560471</v>
+        <v>1.813977409660765</v>
       </c>
       <c r="F11" t="n">
-        <v>11.33598845234264</v>
+        <v>1.842098123505679</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
